--- a/estudo-mercado-gtk/planilha-capacidade-financeiro.xlsx
+++ b/estudo-mercado-gtk/planilha-capacidade-financeiro.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premissas" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacidade" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custo Unitário" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cenários" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX e Funding" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix e Memória" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cenários" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX e Funding" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -160,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,10 +190,12 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -963,7 +966,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Estudo §13.4 — mix vedação+estrutural+paver</t>
+          <t>derivada 36,5% na aba 'Mix e Memória'; adotada 35% (conservador)</t>
         </is>
       </c>
       <c r="D27" s="4" t="n"/>
@@ -1525,6 +1528,325 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MIX DE PRODUÇÃO → RECEITA PLENA DE 1 TURNO E MC MÉDIA (derivadas, não afirmadas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Premissa de mix em % dos 264 dias úteis/ano (editável em azul). Base do estudo §5.4 e Apêndice A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>% dos dias</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Dias/ano</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Capacidade/turno</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Quantidade/ano</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Preço (R$)</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>Receita (R$)</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>MC do produto (%)</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>MC (R$)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Bloco 14 vedação</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C4" s="26">
+        <f>B4*Premissas!$B$9*12</f>
+        <v/>
+      </c>
+      <c r="D4" s="18">
+        <f>Premissas!$B$5</f>
+        <v/>
+      </c>
+      <c r="E4" s="19">
+        <f>C4*D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="22">
+        <f>Premissas!$B$11</f>
+        <v/>
+      </c>
+      <c r="G4" s="27">
+        <f>E4*F4</f>
+        <v/>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I4" s="27">
+        <f>G4*H4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Bloco 14 estrutural fbk 6–8</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C5" s="26">
+        <f>B5*Premissas!$B$9*12</f>
+        <v/>
+      </c>
+      <c r="D5" s="18">
+        <f>Premissas!$B$5</f>
+        <v/>
+      </c>
+      <c r="E5" s="19">
+        <f>C5*D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="22">
+        <f>Premissas!$B$12</f>
+        <v/>
+      </c>
+      <c r="G5" s="27">
+        <f>E5*F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I5" s="27">
+        <f>G5*H5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Bloco 9 vedação</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C6" s="26">
+        <f>B6*Premissas!$B$9*12</f>
+        <v/>
+      </c>
+      <c r="D6" s="18">
+        <f>Premissas!$B$6</f>
+        <v/>
+      </c>
+      <c r="E6" s="19">
+        <f>C6*D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="22">
+        <f>Premissas!$B$13</f>
+        <v/>
+      </c>
+      <c r="G6" s="27">
+        <f>E6*F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I6" s="27">
+        <f>G6*H6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Bloco 19/canaleta</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="26">
+        <f>B7*Premissas!$B$9*12</f>
+        <v/>
+      </c>
+      <c r="D7" s="18">
+        <f>Premissas!$B$7</f>
+        <v/>
+      </c>
+      <c r="E7" s="19">
+        <f>C7*D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="22">
+        <f>Premissas!$B$14</f>
+        <v/>
+      </c>
+      <c r="G7" s="27">
+        <f>E7*F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I7" s="27">
+        <f>G7*H7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Paver e=6 (m²)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C8" s="26">
+        <f>B8*Premissas!$B$9*12</f>
+        <v/>
+      </c>
+      <c r="D8" s="18">
+        <f>Premissas!$B$8</f>
+        <v/>
+      </c>
+      <c r="E8" s="19">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="22">
+        <f>Premissas!$B$15</f>
+        <v/>
+      </c>
+      <c r="G8" s="27">
+        <f>E8*F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I8" s="27">
+        <f>G8*H8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>TOTAL / MÉDIA PONDERADA</t>
+        </is>
+      </c>
+      <c r="B9" s="25">
+        <f>SUM(B4:B8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="28">
+        <f>SUM(G4:G8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="27">
+        <f>SUM(I4:I8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>MC média derivada (I9 ÷ G9)</t>
+        </is>
+      </c>
+      <c r="B10" s="25">
+        <f>I9/G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>MC adotada no modelo (Premissas) — conservadora</t>
+        </is>
+      </c>
+      <c r="B11" s="29">
+        <f>Premissas!$B$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Notas: MC% por produto conforme estudo §13.2 (vedação 31% calculada na aba 'Custo Unitário'; estrutural/paver com traço mais rico).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1545,17 +1867,18 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>Receita anual a 100% de 1 turno (mix do estudo §5.4/§13):</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="n">
-        <v>7000000</v>
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Receita anual a 100% de 1 turno (derivada na aba 'Mix e Memória'):</t>
+        </is>
+      </c>
+      <c r="B3" s="31">
+        <f>'Mix e Memória'!$G$9</f>
+        <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>mix: 60% bloco14 (ved+estr), 15% bloco 9, 10% bloco 19/canaleta, 15% paver</t>
+          <t>mix: 40% bloco14 ved., 20% bloco14 estr., 15% bloco 9, 10% bloco 19/canaleta, 15% paver</t>
         </is>
       </c>
     </row>
@@ -1609,11 +1932,11 @@
         <f>$B$3*B6</f>
         <v/>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="31">
         <f>C6*Premissas!$B$27</f>
         <v/>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="31">
         <f>Premissas!$B$26*12</f>
         <v/>
       </c>
@@ -1639,11 +1962,11 @@
         <f>$B$3*B7</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="31">
         <f>C7*Premissas!$B$27</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="31">
         <f>Premissas!$B$26*12</f>
         <v/>
       </c>
@@ -1669,11 +1992,11 @@
         <f>$B$3*B8</f>
         <v/>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="31">
         <f>C8*Premissas!$B$27</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f>Premissas!$B$26*12</f>
         <v/>
       </c>
@@ -1699,11 +2022,11 @@
         <f>$B$3*B9</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="31">
         <f>C9*Premissas!$B$27</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="31">
         <f>Premissas!$B$26*12</f>
         <v/>
       </c>
@@ -1729,11 +2052,11 @@
         <f>$B$3*B10</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="31">
         <f>C10*Premissas!$B$27</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="31">
         <f>Premissas!$B$26*12</f>
         <v/>
       </c>
@@ -1805,7 +2128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2010,7 +2333,7 @@
           <t>INVESTIMENTO TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="28">
         <f>B13+B14</f>
         <v/>
       </c>

--- a/estudo-mercado-gtk/planilha-capacidade-financeiro.xlsx
+++ b/estudo-mercado-gtk/planilha-capacidade-financeiro.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premissas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacidade" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix e Plano" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custo Unitário" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix e Memória" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cenários" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX e Funding" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cenários e DSCR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX e Funding" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,12 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="R$ #,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -161,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,31 +169,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -561,27 +556,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GTK PRÉ-MOLDADOS — PREMISSAS DO MODELO (edite apenas as células AZUIS; amarelas = premissas-chave)</t>
+          <t>GTK PRÉ-MOLDADOS — PREMISSAS (edite as células AZUIS; amarelas = premissas-chave)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fontes: proposta Gervasi REV00 12/05/2026; SINAPI-ES 06/2026; referências do Estudo de Mercado ago/2026 (ver fontes.md)</t>
+          <t>Fontes: proposta Gervasi REV00 12/05/2026; SINAPI-ES 06/2026; Estudo de Mercado v3 ago/2026 (refs. em fontes.md)</t>
         </is>
       </c>
     </row>
@@ -593,7 +588,8 @@
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -657,81 +653,76 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Proposta Gervasi p.3 (dígitos comprimidos; ver estudo §3.3)</t>
+          <t>Proposta Gervasi p.3 (ver estudo §3.3)</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Dias úteis/mês</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>premissa</t>
-        </is>
-      </c>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Calendário e capacidade efetiva (estudo §3.7)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Preços de venda posto fábrica (R$/un ou R$/m²)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Dias úteis na planta (2027, já sem feriados locais)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>249</v>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>252 nacionais − 3 locais [141][142]</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Bloco 14 vedação</t>
+          <t>Dias efetivos de produção vendável/ano (OEE ~76%)</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>3.3</v>
+        <v>210</v>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Estudo §6.4 (10–25% abaixo da mediana SINAPI-ES)</t>
+          <t>cascata §3.7: manutenção, trocas, corretivas, refugo</t>
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Bloco 14 estrutural fbk 6–8</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Estudo §6.4</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Preços de venda posto fábrica</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Bloco 9 vedação</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>2.8</v>
+          <t>Bloco 14 vedação (R$/un)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>3.3</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
@@ -744,11 +735,11 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bloco 19 estrutural</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>5.5</v>
+          <t>Bloco 14 estrutural fbk 6–8 (R$/un)</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>4.5</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
@@ -761,11 +752,11 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Paver 35 MPa e=6 (m²)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>57</v>
+          <t>Bloco 9 vedação (R$/un)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>2.8</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
@@ -776,61 +767,62 @@
       <c r="E15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Custos de insumos (posto fábrica)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Bloco 19/canaleta (R$/un)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Estudo §6.4</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Cimento a granel (R$/kg)</t>
+          <t>Paver 35 MPa e=6 (R$/m²)</t>
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>0.55</v>
+        <v>57</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>R$ 450/t + frete — ref. nacional 2025 [fontes.md]</t>
+          <t>Estudo §6.4</t>
         </is>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Agregados mix (R$/m³)</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>165</v>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>SINAPI-ES 06/2026 + frete</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Custos variáveis industriais (sem tributos/frete)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Consumo cimento bloco 14 vedação (kg/un)</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>1</v>
+          <t>CV industrial — bloco 14 vedação (R$/un)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1.85</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>WM Máquinas + traço típico; Gervasi economiza até 15%</t>
+          <t>Estudo §13.2 (cimento 0,55 + agregados 0,89 + MO/energia/manut.)</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
@@ -839,15 +831,15 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Consumo concreto bloco 14 (m³/un)</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>0.0054</v>
+          <t>CV industrial — bloco 14 estrutural (R$/un)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>2.1</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>5,4 m³/h ÷ 1.000 pç/h (proposta)</t>
+          <t>traço mais rico</t>
         </is>
       </c>
       <c r="D20" s="4" t="n"/>
@@ -856,15 +848,15 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Aditivo+energia+diesel (R$/un bloco 14)</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>0.12</v>
+          <t>CV industrial — bloco 9 (R$/un)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>1.45</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Estudo §13.2</t>
+          <t>proporcional ao volume de concreto</t>
         </is>
       </c>
       <c r="D21" s="4" t="n"/>
@@ -873,15 +865,15 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mão de obra direta (R$/mês, 6 pessoas c/ encargos)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n">
-        <v>32000</v>
+          <t>CV industrial — bloco 19/canaleta (R$/un)</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>2.45</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>CCT construção ES 2025/27 + encargos</t>
+          <t>proporcional</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
@@ -890,49 +882,43 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Manutenção e moldes (R$/un)</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>0.08</v>
+          <t>CV industrial — paver e=6 (R$/m²)</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>24</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>provisão</t>
+          <t>incl. pigmento parcial</t>
         </is>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Tributos s/ receita (Simples ind.)</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>faixa relevante — validar c/ contador</t>
-        </is>
-      </c>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Tributos e comercial</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Frete médio embutido s/ receita</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="n">
-        <v>0.045</v>
+          <t>Carga tributária s/ receita (premissa conservadora)</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>0.15</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>parcela CIF do mix</t>
+          <t>cobre Simples Anexo II topo (15% [140]) e L. Presumido típico — definir c/ contador</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
@@ -941,15 +927,15 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Custo fixo desembolsável (R$/mês)</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n">
-        <v>52000</v>
+          <t>Frete médio embutido s/ receita</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>0.045</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Estudo §13.3</t>
+          <t>parcela CIF do mix</t>
         </is>
       </c>
       <c r="D26" s="4" t="n"/>
@@ -958,64 +944,112 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Margem de contribuição média do mix (% receita)</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>0.35</v>
+          <t>MC média adotada (% receita)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0.3</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>derivada 36,5% na aba 'Mix e Memória'; adotada 35% (conservador)</t>
+          <t>derivada 31,2% na aba 'Mix e Plano' — adotada 30% (conservadora)</t>
         </is>
       </c>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Serviço da dívida FNE estimado (R$/mês, SAC pós-carência)</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>≈R$ 5 mi, 10 anos SAC — substituir pela simulação BNB</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Estrutura de resultado e dívida</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="5" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Custo fixo desembolsável (R$/mês)</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>52000</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Estudo §13.3</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Serviço da dívida FNE (R$/mês, SAC pós-carência)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>recomendação §13.4: ~R$ 4,0–4,5 mi em 12 anos — substituir pela simulação BNB</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>TETO DE RECEITA — pequena empresa EPP (R$/ano)</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>LC 123/2006, art. 3º, II [139]</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="5" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A4:D4"/>
+  <mergeCells count="28">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C12:E12"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C20:E20"/>
+    <mergeCell ref="A9:E9"/>
     <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1027,204 +1061,406 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CAPACIDADE DE PRODUÇÃO — LINHA GERVASI XP350</t>
+          <t>PLANO DE VENDAS — MIX PELA ABSORÇÃO DO MERCADO, LIMITADO AO TETO EPP (estudo §5.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Método em 3 passos: capacidade máxima por produto (§3.3) → horas alocadas na proporção do mercado → escala até o teto de R$ 4,8 mi. Volumes em AZUL.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>Peças/bandeja</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>Peças/hora</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>Por turno 8h (90%)</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>Por mês (1 turno)</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>Por ano (1 turno)</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>Por ano (2 turnos)</t>
-        </is>
-      </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t>Concreto (m³/h)</t>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>% do mercado (valor)</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Vendas/ano (un ou m²)</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Capacidade/turno</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Dias de produção</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Preço (R$)</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>Receita (R$)</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>% da receita</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>MC do produto (%)</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>MC (R$)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Bloco 14×19×39 (un)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>4</v>
+          <t>Bloco 14 vedação</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>0.36</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D4" s="18">
+        <v>522655</v>
+      </c>
+      <c r="D4" s="16">
         <f>Premissas!$B$5</f>
         <v/>
       </c>
-      <c r="E4" s="19">
-        <f>D4*Premissas!$B$9</f>
-        <v/>
-      </c>
-      <c r="F4" s="19">
-        <f>E4*12</f>
+      <c r="E4" s="17">
+        <f>C4/D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="18">
+        <f>Premissas!$B$13</f>
         <v/>
       </c>
       <c r="G4" s="19">
-        <f>F4*2</f>
-        <v/>
-      </c>
-      <c r="H4" s="20" t="n">
-        <v>5.4</v>
+        <f>C4*F4</f>
+        <v/>
+      </c>
+      <c r="H4" s="20">
+        <f>G4/$G$9</f>
+        <v/>
+      </c>
+      <c r="I4" s="20">
+        <f>(F4*(1-Premissas!$B$25-Premissas!$B$26)-Premissas!$B$19)/F4</f>
+        <v/>
+      </c>
+      <c r="J4" s="19">
+        <f>G4*I4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Bloco 9×19×39 (un)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>6</v>
+          <t>Bloco 14 estrutural fbk 6–8</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>0.26</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D5" s="18">
-        <f>Premissas!$B$6</f>
-        <v/>
-      </c>
-      <c r="E5" s="19">
-        <f>D5*Premissas!$B$9</f>
-        <v/>
-      </c>
-      <c r="F5" s="19">
-        <f>E5*12</f>
+        <v>276813</v>
+      </c>
+      <c r="D5" s="16">
+        <f>Premissas!$B$5</f>
+        <v/>
+      </c>
+      <c r="E5" s="17">
+        <f>C5/D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>Premissas!$B$14</f>
         <v/>
       </c>
       <c r="G5" s="19">
-        <f>F5*2</f>
-        <v/>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>7.3</v>
+        <f>C5*F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="20">
+        <f>G5/$G$9</f>
+        <v/>
+      </c>
+      <c r="I5" s="20">
+        <f>(F5*(1-Premissas!$B$25-Premissas!$B$26)-Premissas!$B$20)/F5</f>
+        <v/>
+      </c>
+      <c r="J5" s="19">
+        <f>G5*I5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bloco 19×19×39 (un)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>3</v>
+          <t>Bloco 9 vedação</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>0.09</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>750</v>
-      </c>
-      <c r="D6" s="18">
-        <f>Premissas!$B$7</f>
-        <v/>
-      </c>
-      <c r="E6" s="19">
-        <f>D6*Premissas!$B$9</f>
-        <v/>
-      </c>
-      <c r="F6" s="19">
-        <f>E6*12</f>
+        <v>153996</v>
+      </c>
+      <c r="D6" s="16">
+        <f>Premissas!$B$6</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>C6/D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>Premissas!$B$15</f>
         <v/>
       </c>
       <c r="G6" s="19">
-        <f>F6*2</f>
-        <v/>
-      </c>
-      <c r="H6" s="20" t="n">
-        <v>4.7</v>
+        <f>C6*F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="20">
+        <f>G6/$G$9</f>
+        <v/>
+      </c>
+      <c r="I6" s="20">
+        <f>(F6*(1-Premissas!$B$25-Premissas!$B$26)-Premissas!$B$21)/F6</f>
+        <v/>
+      </c>
+      <c r="J6" s="19">
+        <f>G6*I6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Paver H6 (m²)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>0.37</v>
+          <t>Bloco 19 + canaletas</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>0.04</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="D7" s="18">
+        <v>34844</v>
+      </c>
+      <c r="D7" s="16">
+        <f>Premissas!$B$7</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>C7/D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>Premissas!$B$16</f>
+        <v/>
+      </c>
+      <c r="G7" s="19">
+        <f>C7*F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="20">
+        <f>G7/$G$9</f>
+        <v/>
+      </c>
+      <c r="I7" s="20">
+        <f>(F7*(1-Premissas!$B$25-Premissas!$B$26)-Premissas!$B$22)/F7</f>
+        <v/>
+      </c>
+      <c r="J7" s="19">
+        <f>G7*I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Paver 35 MPa e=6/8 (m²)</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>21013</v>
+      </c>
+      <c r="D8" s="16">
         <f>Premissas!$B$8</f>
         <v/>
       </c>
-      <c r="E7" s="19">
-        <f>D7*Premissas!$B$9</f>
-        <v/>
-      </c>
-      <c r="F7" s="19">
-        <f>E7*12</f>
-        <v/>
-      </c>
-      <c r="G7" s="19">
-        <f>F7*2</f>
-        <v/>
-      </c>
-      <c r="H7" s="20" t="n">
-        <v>4.1</v>
+      <c r="E8" s="17">
+        <f>C8/D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="18">
+        <f>Premissas!$B$17</f>
+        <v/>
+      </c>
+      <c r="G8" s="19">
+        <f>C8*F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="20">
+        <f>G8/$G$9</f>
+        <v/>
+      </c>
+      <c r="I8" s="20">
+        <f>(F8*(1-Premissas!$B$25-Premissas!$B$26)-Premissas!$B$23)/F8</f>
+        <v/>
+      </c>
+      <c r="J8" s="19">
+        <f>G8*I8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Nota: valores por turno conforme proposta Gervasi (fator 90%). Troca de molde: 15–20 min. Silo 90 t ≈ 13 dias úteis de autonomia em produção plena de bloco 14.</t>
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>TOTAL — PLANO-BASE</t>
+        </is>
+      </c>
+      <c r="B9" s="20">
+        <f>SUM(B4:B8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>SUM(E4:E8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>SUM(G4:G8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="19">
+        <f>SUM(J4:J8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Verificação do teto EPP (R$ 4,8 mi)</t>
+        </is>
+      </c>
+      <c r="B10" s="6">
+        <f>IF(G9&lt;=Premissas!$B$31,"OK — dentro do teto (folga de "&amp;TEXT(Premissas!$B$31-G9,"R$ #,##0")&amp;")","ULTRAPASSOU O TETO!")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>R$ por dia de produção no mix</t>
+        </is>
+      </c>
+      <c r="B11" s="19">
+        <f>G9/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>CAPACIDADE EFETIVA anual (× dias efetivos §3.7)</t>
+        </is>
+      </c>
+      <c r="B12" s="19">
+        <f>(G9/E9)*Premissas!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Utilização do plano-base (÷ capacidade efetiva)</t>
+        </is>
+      </c>
+      <c r="B13" s="20">
+        <f>G9/B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Folga (dias efetivos não usados)</t>
+        </is>
+      </c>
+      <c r="B14" s="23">
+        <f>Premissas!$B$11-E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>MC média ponderada derivada (J9 ÷ G9)</t>
+        </is>
+      </c>
+      <c r="B15" s="20">
+        <f>J9/G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>MC adotada no modelo (Premissas — conservadora)</t>
+        </is>
+      </c>
+      <c r="B16" s="24">
+        <f>Premissas!$B$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Nota: capacidade efetiva usa a célula B12 (=R$/dia × 210 dias efetivos). % de mercado por produto: paver 25% (R$ 3,9–8,3 mi de um SAM de 16–25 mi), estrutural+complementos 30%, vedação 45% — estudo §5.4/Apêndice A.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B10:E10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1235,288 +1471,191 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CUSTO VARIÁVEL E MARGEM POR PRODUTO (bloco 14 vedação detalhado; demais derivados)</t>
+          <t>CUSTO VARIÁVEL DETALHADO — BLOCO 14 VEDAÇÃO (demais produtos na aba 'Mix e Plano')</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>Bloco 14×19×39 — vedação</t>
-        </is>
-      </c>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Cimento a granel: 1,00 kg × R$ 0,55/kg</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>1,05 kg ref. WM; Gervasi economiza até 15%; granel R$ 450/t + frete [93]</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Cimento (kg × R$/kg)</t>
-        </is>
-      </c>
-      <c r="B4" s="22">
-        <f>Premissas!$B$19*Premissas!$B$17</f>
-        <v/>
-      </c>
+          <t>Agregados: 0,0054 m³ × R$ 165/m³ (posto fábrica)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>SINAPI-ES 06/2026 + frete [11]</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Agregados (m³ × R$/m³)</t>
-        </is>
-      </c>
-      <c r="B5" s="22">
-        <f>Premissas!$B$20*Premissas!$B$18</f>
-        <v/>
-      </c>
+          <t>Aditivo + energia + diesel</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>estudo §13.2</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Aditivo + energia + diesel</t>
-        </is>
-      </c>
-      <c r="B6" s="22">
-        <f>Premissas!$B$21</f>
-        <v/>
-      </c>
+          <t>Mão de obra direta (rateio)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>R$ 32 mil/mês ÷ 154,4 mil blocos</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Mão de obra direta (rateio mensal ÷ produção)</t>
-        </is>
-      </c>
-      <c r="B7" s="22">
-        <f>Premissas!$B$22/(Premissas!$B$5*Premissas!$B$9)</f>
-        <v/>
-      </c>
+          <t>Manutenção e moldes (provisão)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>estudo §13.2</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Manutenção e moldes</t>
-        </is>
-      </c>
-      <c r="B8" s="22">
-        <f>Premissas!$B$23</f>
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>CV INDUSTRIAL (soma) → alimenta Premissas!B19</t>
+        </is>
+      </c>
+      <c r="B8" s="25">
+        <f>SUM(B3:B7)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>CUSTO VARIÁVEL INDUSTRIAL (un)</t>
-        </is>
-      </c>
-      <c r="B9" s="23">
-        <f>SUM(B4:B8)</f>
+          <t>Tributos (15% × PV)</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>Premissas!$B$25*Premissas!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Tributos sobre venda (% × PV)</t>
-        </is>
-      </c>
-      <c r="B10" s="22">
-        <f>Premissas!$B$24*Premissas!$B$11</f>
+          <t>Frete embutido (4,5% × PV)</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
+        <f>Premissas!$B$26*Premissas!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Frete embutido (% × PV)</t>
-        </is>
-      </c>
-      <c r="B11" s="22">
-        <f>Premissas!$B$25*Premissas!$B$11</f>
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>CUSTO VARIÁVEL TOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="25">
+        <f>B8+B9+B10</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>CUSTO VARIÁVEL TOTAL (un)</t>
-        </is>
-      </c>
-      <c r="B12" s="23">
-        <f>B9+B10+B11</f>
+          <t>Preço de venda</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>Premissas!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Preço de venda — bloco 14 vedação</t>
-        </is>
-      </c>
-      <c r="B13" s="22">
-        <f>Premissas!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>MARGEM DE CONTRIBUIÇÃO (R$/un)</t>
-        </is>
-      </c>
-      <c r="B14" s="23">
-        <f>B13-B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>MARGEM DE CONTRIBUIÇÃO (%)</t>
-        </is>
-      </c>
-      <c r="B15" s="25">
-        <f>B14/B13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>Margens indicativas dos demais produtos (traço mais rico no estrutural/paver — estudo §13.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>PV (R$)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>CV total (R$)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>MC (R$)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>MC (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Bloco 9 vedação</t>
-        </is>
-      </c>
-      <c r="B19" s="22">
-        <f>Premissas!$B$13</f>
-        <v/>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="D19" s="23">
-        <f>B19-C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="25">
-        <f>D19/B19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Bloco 14 estrutural fbk 6–8</t>
-        </is>
-      </c>
-      <c r="B20" s="22">
-        <f>Premissas!$B$12</f>
-        <v/>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="D20" s="23">
-        <f>B20-C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="25">
-        <f>D20/B20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Bloco 19 estrutural</t>
-        </is>
-      </c>
-      <c r="B21" s="22">
-        <f>Premissas!$B$14</f>
-        <v/>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D21" s="23">
-        <f>B21-C21</f>
-        <v/>
-      </c>
-      <c r="E21" s="25">
-        <f>D21/B21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Paver e=6 (m²)</t>
-        </is>
-      </c>
-      <c r="B22" s="22">
-        <f>Premissas!$B$15</f>
-        <v/>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D22" s="23">
-        <f>B22-C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="25">
-        <f>D22/B22</f>
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>MARGEM DE CONTRIBUIÇÃO (R$/un | %)</t>
+        </is>
+      </c>
+      <c r="B13" s="25">
+        <f>B12-B11</f>
+        <v/>
+      </c>
+      <c r="C13" s="20">
+        <f>B13/B12</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A3:B3"/>
+  <mergeCells count="5">
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1528,607 +1667,272 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MIX DE PRODUÇÃO → RECEITA PLENA DE 1 TURNO E MC MÉDIA (derivadas, não afirmadas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Premissa de mix em % dos 264 dias úteis/ano (editável em azul). Base do estudo §5.4 e Apêndice A.</t>
+          <t>CENÁRIOS (base = teto EPP), PONTO DE EQUILÍBRIO E CAPACIDADE DE PAGAMENTO</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>% dos dias</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>Dias/ano</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>Capacidade/turno</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>Quantidade/ano</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>Preço (R$)</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>Receita (R$)</t>
-        </is>
-      </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t>MC do produto (%)</t>
-        </is>
-      </c>
-      <c r="I3" s="17" t="inlineStr">
-        <is>
-          <t>MC (R$)</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Cenário</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Receita anual</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>% da capacidade efetiva</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Margem contrib. (MC adotada)</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Custos fixos ano</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>DSCR (EBITDA ÷ dívida)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Bloco 14 vedação</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C4" s="26">
-        <f>B4*Premissas!$B$9*12</f>
-        <v/>
-      </c>
-      <c r="D4" s="18">
-        <f>Premissas!$B$5</f>
-        <v/>
-      </c>
-      <c r="E4" s="19">
-        <f>C4*D4</f>
-        <v/>
-      </c>
-      <c r="F4" s="22">
-        <f>Premissas!$B$11</f>
+          <t>Ano 1 — ramp-up (piso)</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="C4" s="20">
+        <f>B4/'Mix e Plano'!$B$12</f>
+        <v/>
+      </c>
+      <c r="D4" s="26">
+        <f>B4*Premissas!$B$27</f>
+        <v/>
+      </c>
+      <c r="E4" s="26">
+        <f>Premissas!$B$29*12</f>
+        <v/>
+      </c>
+      <c r="F4" s="19">
+        <f>D4-E4</f>
         <v/>
       </c>
       <c r="G4" s="27">
-        <f>E4*F4</f>
-        <v/>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I4" s="27">
-        <f>G4*H4</f>
+        <f>F4/(Premissas!$B$30*12)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Bloco 14 estrutural fbk 6–8</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C5" s="26">
-        <f>B5*Premissas!$B$9*12</f>
-        <v/>
-      </c>
-      <c r="D5" s="18">
-        <f>Premissas!$B$5</f>
-        <v/>
-      </c>
-      <c r="E5" s="19">
-        <f>C5*D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="22">
-        <f>Premissas!$B$12</f>
+          <t>Ano 1 — ramp-up (topo)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="C5" s="20">
+        <f>B5/'Mix e Plano'!$B$12</f>
+        <v/>
+      </c>
+      <c r="D5" s="26">
+        <f>B5*Premissas!$B$27</f>
+        <v/>
+      </c>
+      <c r="E5" s="26">
+        <f>Premissas!$B$29*12</f>
+        <v/>
+      </c>
+      <c r="F5" s="19">
+        <f>D5-E5</f>
         <v/>
       </c>
       <c r="G5" s="27">
-        <f>E5*F5</f>
-        <v/>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I5" s="27">
-        <f>G5*H5</f>
+        <f>F5/(Premissas!$B$30*12)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bloco 9 vedação</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C6" s="26">
-        <f>B6*Premissas!$B$9*12</f>
-        <v/>
-      </c>
-      <c r="D6" s="18">
-        <f>Premissas!$B$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="19">
-        <f>C6*D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="22">
-        <f>Premissas!$B$13</f>
+          <t>Ano 2</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="C6" s="20">
+        <f>B6/'Mix e Plano'!$B$12</f>
+        <v/>
+      </c>
+      <c r="D6" s="26">
+        <f>B6*Premissas!$B$27</f>
+        <v/>
+      </c>
+      <c r="E6" s="26">
+        <f>Premissas!$B$29*12</f>
+        <v/>
+      </c>
+      <c r="F6" s="19">
+        <f>D6-E6</f>
         <v/>
       </c>
       <c r="G6" s="27">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I6" s="27">
-        <f>G6*H6</f>
+        <f>F6/(Premissas!$B$30*12)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Bloco 19/canaleta</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C7" s="26">
-        <f>B7*Premissas!$B$9*12</f>
-        <v/>
-      </c>
-      <c r="D7" s="18">
-        <f>Premissas!$B$7</f>
-        <v/>
-      </c>
-      <c r="E7" s="19">
-        <f>C7*D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="22">
-        <f>Premissas!$B$14</f>
+          <t>Ano 3+ — regime (teto EPP)</t>
+        </is>
+      </c>
+      <c r="B7" s="26">
+        <f>'Mix e Plano'!$G$9</f>
+        <v/>
+      </c>
+      <c r="C7" s="20">
+        <f>B7/'Mix e Plano'!$B$12</f>
+        <v/>
+      </c>
+      <c r="D7" s="26">
+        <f>B7*Premissas!$B$27</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>Premissas!$B$29*12</f>
+        <v/>
+      </c>
+      <c r="F7" s="19">
+        <f>D7-E7</f>
         <v/>
       </c>
       <c r="G7" s="27">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I7" s="27">
-        <f>G7*H7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Paver e=6 (m²)</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C8" s="26">
-        <f>B8*Premissas!$B$9*12</f>
-        <v/>
-      </c>
-      <c r="D8" s="18">
-        <f>Premissas!$B$8</f>
-        <v/>
-      </c>
-      <c r="E8" s="19">
-        <f>C8*D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="22">
-        <f>Premissas!$B$15</f>
-        <v/>
-      </c>
-      <c r="G8" s="27">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I8" s="27">
-        <f>G8*H8</f>
+        <f>F7/(Premissas!$B$30*12)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>TOTAL / MÉDIA PONDERADA</t>
-        </is>
-      </c>
-      <c r="B9" s="25">
-        <f>SUM(B4:B8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="28">
-        <f>SUM(G4:G8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="27">
-        <f>SUM(I4:I8)</f>
-        <v/>
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Ponto de equilíbrio e dívida</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>MC média derivada (I9 ÷ G9)</t>
-        </is>
-      </c>
-      <c r="B10" s="25">
-        <f>I9/G9</f>
+          <t>Receita de equilíbrio operacional (R$/mês)</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>Premissas!$B$29/Premissas!$B$27</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>MC adotada no modelo (Premissas) — conservadora</t>
-        </is>
-      </c>
-      <c r="B11" s="29">
-        <f>Premissas!$B$27</f>
+          <t>Equilíbrio ÷ capacidade efetiva</t>
+        </is>
+      </c>
+      <c r="B11" s="20">
+        <f>B10*12/'Mix e Plano'!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Equilíbrio ÷ teto EPP</t>
+        </is>
+      </c>
+      <c r="B12" s="20">
+        <f>B10*12/Premissas!$B$31</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Notas: MC% por produto conforme estudo §13.2 (vedação 31% calculada na aba 'Custo Unitário'; estrutural/paver com traço mais rico).</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Serviço anual da dívida (Premissas!B30 × 12)</t>
+        </is>
+      </c>
+      <c r="B13" s="26">
+        <f>Premissas!$B$30*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>DSCR no regime (meta ≥ 1,35)</t>
+        </is>
+      </c>
+      <c r="B14" s="27">
+        <f>F7/B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Payback bruto (investimento ~R$ 7,4 mi ÷ EBITDA regime)</t>
+        </is>
+      </c>
+      <c r="B15" s="17">
+        <f>7378000/F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Recomendação (estudo §13.4): dívida FNE de ~R$ 4,0–4,5 mi em 12 anos (parcela média R$ 46–50 mil/mês) → DSCR 1,36–1,47; carência cobre o ano 1; bônus de adimplência dá folga adicional.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:C9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CENÁRIOS DE UTILIZAÇÃO (1 turno) — RECEITA, EBITDA E PONTO DE EQUILÍBRIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="30" t="inlineStr">
-        <is>
-          <t>Receita anual a 100% de 1 turno (derivada na aba 'Mix e Memória'):</t>
-        </is>
-      </c>
-      <c r="B3" s="31">
-        <f>'Mix e Memória'!$G$9</f>
-        <v/>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>mix: 40% bloco14 ved., 20% bloco14 estr., 15% bloco 9, 10% bloco 19/canaleta, 15% paver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Cenário</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Utilização</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Receita anual</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Margem contribuição</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>Custos fixos ano</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>EBITDA – dívida FNE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Pessimista (ano 1 fraco)</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C6" s="27">
-        <f>$B$3*B6</f>
-        <v/>
-      </c>
-      <c r="D6" s="31">
-        <f>C6*Premissas!$B$27</f>
-        <v/>
-      </c>
-      <c r="E6" s="31">
-        <f>Premissas!$B$26*12</f>
-        <v/>
-      </c>
-      <c r="F6" s="27">
-        <f>D6-E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="27">
-        <f>F6-Premissas!$B$28*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Base ano 1</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="C7" s="27">
-        <f>$B$3*B7</f>
-        <v/>
-      </c>
-      <c r="D7" s="31">
-        <f>C7*Premissas!$B$27</f>
-        <v/>
-      </c>
-      <c r="E7" s="31">
-        <f>Premissas!$B$26*12</f>
-        <v/>
-      </c>
-      <c r="F7" s="27">
-        <f>D7-E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="27">
-        <f>F7-Premissas!$B$28*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Base ano 2</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C8" s="27">
-        <f>$B$3*B8</f>
-        <v/>
-      </c>
-      <c r="D8" s="31">
-        <f>C8*Premissas!$B$27</f>
-        <v/>
-      </c>
-      <c r="E8" s="31">
-        <f>Premissas!$B$26*12</f>
-        <v/>
-      </c>
-      <c r="F8" s="27">
-        <f>D8-E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="27">
-        <f>F8-Premissas!$B$28*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Base ano 3 (regime)</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="C9" s="27">
-        <f>$B$3*B9</f>
-        <v/>
-      </c>
-      <c r="D9" s="31">
-        <f>C9*Premissas!$B$27</f>
-        <v/>
-      </c>
-      <c r="E9" s="31">
-        <f>Premissas!$B$26*12</f>
-        <v/>
-      </c>
-      <c r="F9" s="27">
-        <f>D9-E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="27">
-        <f>F9-Premissas!$B$28*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Pleno 1 turno</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C10" s="27">
-        <f>$B$3*B10</f>
-        <v/>
-      </c>
-      <c r="D10" s="31">
-        <f>C10*Premissas!$B$27</f>
-        <v/>
-      </c>
-      <c r="E10" s="31">
-        <f>Premissas!$B$26*12</f>
-        <v/>
-      </c>
-      <c r="F10" s="27">
-        <f>D10-E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="27">
-        <f>F10-Premissas!$B$28*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Ponto de equilíbrio</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Receita de equilíbrio operacional (R$/mês)</t>
-        </is>
-      </c>
-      <c r="B14" s="27">
-        <f>Premissas!$B$26/Premissas!$B$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Equilíbrio operacional (% da capacidade de 1 turno)</t>
-        </is>
-      </c>
-      <c r="B15" s="25">
-        <f>B14*12/$B$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Receita de equilíbrio com dívida FNE (R$/mês)</t>
-        </is>
-      </c>
-      <c r="B16" s="27">
-        <f>(Premissas!$B$26+Premissas!$B$28)/Premissas!$B$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Equilíbrio com dívida (% da capacidade de 1 turno)</t>
-        </is>
-      </c>
-      <c r="B17" s="25">
-        <f>B16*12/$B$3</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A13:C13"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2150,17 +1954,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
@@ -2237,7 +2041,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>faixa 280–420 mil — item não incluso na proposta</t>
+          <t>faixa 280–420 mil — não incluso na proposta</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2106,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPEX</t>
         </is>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="19">
         <f>SUM(B4:B12)</f>
         <v/>
       </c>
@@ -2328,12 +2132,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>INVESTIMENTO TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="22">
         <f>B13+B14</f>
         <v/>
       </c>
@@ -2341,7 +2145,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Funding indicativo</t>
+          <t>Funding indicativo (§13.4: DSCR ≥1,35)</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -2350,16 +2154,15 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>FNE/BNB (equipamentos + obras civis financiáveis)</t>
-        </is>
-      </c>
-      <c r="B18" s="27">
-        <f>0.65*B15</f>
-        <v/>
+          <t>FNE/BNB — recomendação ~R$ 4,0–4,5 mi em 12 anos</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>4500000</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>≈65% — calibrar no projeto de crédito</t>
+          <t>calibrar na simulação de capacidade de pagamento</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2172,7 @@
           <t>Recursos próprios (capital social subscrito R$ 7,5 mi)</t>
         </is>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="19">
         <f>B15-B18</f>
         <v/>
       </c>
